--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2018_T1_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2018_T1_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>91</t>
+    <t>87</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>10.471</t>
-  </si>
-  <si>
-    <t>(6.178)</t>
-  </si>
-  <si>
-    <t>14.934</t>
-  </si>
-  <si>
-    <t>(1.545)</t>
-  </si>
-  <si>
-    <t>81.891</t>
-  </si>
-  <si>
-    <t>(20.385)</t>
-  </si>
-  <si>
-    <t>123.204</t>
-  </si>
-  <si>
-    <t>(42.130)</t>
-  </si>
-  <si>
-    <t>2.988</t>
-  </si>
-  <si>
-    <t>(0.396)</t>
-  </si>
-  <si>
-    <t>17.165</t>
-  </si>
-  <si>
-    <t>(1.900)</t>
-  </si>
-  <si>
-    <t>26.841</t>
-  </si>
-  <si>
-    <t>(18.447)</t>
-  </si>
-  <si>
-    <t>1.014</t>
-  </si>
-  <si>
-    <t>(0.264)</t>
-  </si>
-  <si>
-    <t>121.340</t>
-  </si>
-  <si>
-    <t>(34.128)</t>
-  </si>
-  <si>
-    <t>129.072</t>
-  </si>
-  <si>
-    <t>(51.411)</t>
+    <t>3.659</t>
+  </si>
+  <si>
+    <t>(0.935)</t>
+  </si>
+  <si>
+    <t>15.506</t>
+  </si>
+  <si>
+    <t>(1.588)</t>
+  </si>
+  <si>
+    <t>60.523</t>
+  </si>
+  <si>
+    <t>(12.837)</t>
+  </si>
+  <si>
+    <t>73.149</t>
+  </si>
+  <si>
+    <t>(13.583)</t>
+  </si>
+  <si>
+    <t>2.796</t>
+  </si>
+  <si>
+    <t>(0.309)</t>
+  </si>
+  <si>
+    <t>17.885</t>
+  </si>
+  <si>
+    <t>(1.952)</t>
+  </si>
+  <si>
+    <t>5.135</t>
+  </si>
+  <si>
+    <t>(1.125)</t>
+  </si>
+  <si>
+    <t>1.035</t>
+  </si>
+  <si>
+    <t>(0.275)</t>
+  </si>
+  <si>
+    <t>83.716</t>
+  </si>
+  <si>
+    <t>(15.878)</t>
+  </si>
+  <si>
+    <t>64.680</t>
+  </si>
+  <si>
+    <t>(12.185)</t>
   </si>
   <si>
     <t>23</t>
@@ -198,7 +198,7 @@
     <t>(31.732)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -210,34 +210,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>-7.373</t>
-  </si>
-  <si>
-    <t>-0.673</t>
-  </si>
-  <si>
-    <t>50.323</t>
-  </si>
-  <si>
-    <t>20.646</t>
-  </si>
-  <si>
-    <t>-0.419</t>
-  </si>
-  <si>
-    <t>-3.643</t>
-  </si>
-  <si>
-    <t>-21.582</t>
-  </si>
-  <si>
-    <t>-0.304</t>
-  </si>
-  <si>
-    <t>39.523</t>
-  </si>
-  <si>
-    <t>-0.888</t>
+    <t>-0.562</t>
+  </si>
+  <si>
+    <t>-1.245</t>
+  </si>
+  <si>
+    <t>71.691**</t>
+  </si>
+  <si>
+    <t>70.701**</t>
+  </si>
+  <si>
+    <t>-0.227</t>
+  </si>
+  <si>
+    <t>-4.363</t>
+  </si>
+  <si>
+    <t>0.124</t>
+  </si>
+  <si>
+    <t>-0.325</t>
+  </si>
+  <si>
+    <t>77.147**</t>
+  </si>
+  <si>
+    <t>63.504**</t>
   </si>
 </sst>
 </file>
